--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/80.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/80.xlsx
@@ -426,13 +426,13 @@
         <v>-14.26658605483744</v>
       </c>
       <c r="E2">
-        <v>-15.38217767479403</v>
+        <v>-16.54531169519015</v>
       </c>
       <c r="F2">
-        <v>0.587290562563785</v>
+        <v>0.2083493296470112</v>
       </c>
       <c r="G2">
-        <v>-11.6765303164111</v>
+        <v>-13.63229468355526</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.22177497334174</v>
       </c>
       <c r="E3">
-        <v>-15.16372408866401</v>
+        <v>-15.85133211046268</v>
       </c>
       <c r="F3">
-        <v>0.01753097945458531</v>
+        <v>-0.4182985536506889</v>
       </c>
       <c r="G3">
-        <v>-10.92141474217658</v>
+        <v>-10.45716038847688</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.91153337663021</v>
       </c>
       <c r="E4">
-        <v>-16.00799466875804</v>
+        <v>-17.78814232964726</v>
       </c>
       <c r="F4">
-        <v>0.6181158145018983</v>
+        <v>-0.6104179182526482</v>
       </c>
       <c r="G4">
-        <v>-10.40961102289633</v>
+        <v>-13.50511676611862</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.43904301526536</v>
       </c>
       <c r="E5">
-        <v>-16.63627062410822</v>
+        <v>-18.76785503883671</v>
       </c>
       <c r="F5">
-        <v>0.7341317750433305</v>
+        <v>-0.3581296066583556</v>
       </c>
       <c r="G5">
-        <v>-10.87538822754409</v>
+        <v>-12.91037063889747</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.82479930868244</v>
       </c>
       <c r="E6">
-        <v>-17.9295031742707</v>
+        <v>-19.8265307492979</v>
       </c>
       <c r="F6">
-        <v>1.115372548949322</v>
+        <v>-0.681394866264898</v>
       </c>
       <c r="G6">
-        <v>-9.74143037452307</v>
+        <v>-11.7037595534716</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.110852328723425</v>
       </c>
       <c r="E7">
-        <v>-18.58451524016217</v>
+        <v>-18.88949890763075</v>
       </c>
       <c r="F7">
-        <v>1.060918404752852</v>
+        <v>-0.09356440680757648</v>
       </c>
       <c r="G7">
-        <v>-9.895188662094519</v>
+        <v>-11.41578512864702</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.318722428518558</v>
       </c>
       <c r="E8">
-        <v>-19.64305056792912</v>
+        <v>-21.14197999294202</v>
       </c>
       <c r="F8">
-        <v>0.8168550698303946</v>
+        <v>-0.4606238860937658</v>
       </c>
       <c r="G8">
-        <v>-10.71938870064255</v>
+        <v>-11.04991687782893</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.500201039348648</v>
       </c>
       <c r="E9">
-        <v>-21.33215325889413</v>
+        <v>-20.56755665049105</v>
       </c>
       <c r="F9">
-        <v>0.6540580202527966</v>
+        <v>0.3878101328668631</v>
       </c>
       <c r="G9">
-        <v>-9.482068994794407</v>
+        <v>-9.800722245131416</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.667423103882067</v>
       </c>
       <c r="E10">
-        <v>-19.95387143839359</v>
+        <v>-21.66833811227556</v>
       </c>
       <c r="F10">
-        <v>1.243343905446407</v>
+        <v>0.5609202753658027</v>
       </c>
       <c r="G10">
-        <v>-8.38515945690337</v>
+        <v>-8.974996045089778</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.1322845127662464</v>
       </c>
       <c r="E11">
-        <v>-20.49005634632378</v>
+        <v>-21.55019022541545</v>
       </c>
       <c r="F11">
-        <v>1.665939991922269</v>
+        <v>0.2750083034808152</v>
       </c>
       <c r="G11">
-        <v>-7.464658959163478</v>
+        <v>-7.727844018989998</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.872889486069189</v>
       </c>
       <c r="E12">
-        <v>-21.18769040957544</v>
+        <v>-23.70758694198766</v>
       </c>
       <c r="F12">
-        <v>1.382176317111575</v>
+        <v>0.719837245450574</v>
       </c>
       <c r="G12">
-        <v>-7.063324833983171</v>
+        <v>-9.35118988744486</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.534367114740924</v>
       </c>
       <c r="E13">
-        <v>-22.20648384945108</v>
+        <v>-24.08230005222635</v>
       </c>
       <c r="F13">
-        <v>1.795289172565786</v>
+        <v>0.08342739889010528</v>
       </c>
       <c r="G13">
-        <v>-6.129651675542518</v>
+        <v>-7.711314465112417</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.070211964166671</v>
       </c>
       <c r="E14">
-        <v>-24.1932657793103</v>
+        <v>-24.67647206982476</v>
       </c>
       <c r="F14">
-        <v>1.299784016860838</v>
+        <v>0.4304632924344359</v>
       </c>
       <c r="G14">
-        <v>-6.323984009243276</v>
+        <v>-8.256124323419197</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.472074502515692</v>
       </c>
       <c r="E15">
-        <v>-24.22688517034325</v>
+        <v>-26.2324013971722</v>
       </c>
       <c r="F15">
-        <v>1.688276580153627</v>
+        <v>0.4126260127088415</v>
       </c>
       <c r="G15">
-        <v>-4.919438716569926</v>
+        <v>-5.529171683447353</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.716178180661446</v>
       </c>
       <c r="E16">
-        <v>-25.57775160920135</v>
+        <v>-27.40443839746741</v>
       </c>
       <c r="F16">
-        <v>1.914594490293586</v>
+        <v>0.906044635870198</v>
       </c>
       <c r="G16">
-        <v>-4.108358369994024</v>
+        <v>-6.244779207216212</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>8.788965131851823</v>
       </c>
       <c r="E17">
-        <v>-25.82753317851644</v>
+        <v>-27.85913794410358</v>
       </c>
       <c r="F17">
-        <v>1.65579952294571</v>
+        <v>0.6707914569553298</v>
       </c>
       <c r="G17">
-        <v>-4.121756147791454</v>
+        <v>-4.343671946925419</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>9.69312416323193</v>
       </c>
       <c r="E18">
-        <v>-26.4367895430344</v>
+        <v>-27.24611841768524</v>
       </c>
       <c r="F18">
-        <v>1.597744031497531</v>
+        <v>1.070270188183522</v>
       </c>
       <c r="G18">
-        <v>-2.82506180769648</v>
+        <v>-5.698141927771754</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>10.41228006182439</v>
       </c>
       <c r="E19">
-        <v>-28.39680819150829</v>
+        <v>-28.65792905973858</v>
       </c>
       <c r="F19">
-        <v>1.591819387667872</v>
+        <v>0.2654522219870536</v>
       </c>
       <c r="G19">
-        <v>-2.603579690028159</v>
+        <v>-6.851337360921479</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>10.95290442017396</v>
       </c>
       <c r="E20">
-        <v>-30.02684146751725</v>
+        <v>-30.3221817495865</v>
       </c>
       <c r="F20">
-        <v>1.985457411479924</v>
+        <v>0.9121609081156251</v>
       </c>
       <c r="G20">
-        <v>-1.764210731819185</v>
+        <v>-4.91269182476089</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>11.31337420456424</v>
       </c>
       <c r="E21">
-        <v>-29.94311451158943</v>
+        <v>-30.60134179402634</v>
       </c>
       <c r="F21">
-        <v>1.791345744836342</v>
+        <v>1.321784859438123</v>
       </c>
       <c r="G21">
-        <v>-1.480208961641728</v>
+        <v>-2.552299339624848</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>11.49539358629597</v>
       </c>
       <c r="E22">
-        <v>-30.9290991572795</v>
+        <v>-31.05868596948299</v>
       </c>
       <c r="F22">
-        <v>1.044413021702143</v>
+        <v>0.5976210762501964</v>
       </c>
       <c r="G22">
-        <v>-1.590996368113438</v>
+        <v>-3.354063811053241</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>11.51219538680987</v>
       </c>
       <c r="E23">
-        <v>-30.70153201720904</v>
+        <v>-30.48999793936275</v>
       </c>
       <c r="F23">
-        <v>1.133309602147589</v>
+        <v>1.136773166984656</v>
       </c>
       <c r="G23">
-        <v>-0.8270482583801404</v>
+        <v>-3.09828775214361</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>11.3745214724956</v>
       </c>
       <c r="E24">
-        <v>-29.32455666145972</v>
+        <v>-33.52552916465835</v>
       </c>
       <c r="F24">
-        <v>1.920153298056778</v>
+        <v>0.8830872349199878</v>
       </c>
       <c r="G24">
-        <v>-1.065450574299676</v>
+        <v>-3.203314809376988</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>11.10746342497323</v>
       </c>
       <c r="E25">
-        <v>-31.49968688224596</v>
+        <v>-32.87632033820771</v>
       </c>
       <c r="F25">
-        <v>1.789792129333296</v>
+        <v>0.9954242466198541</v>
       </c>
       <c r="G25">
-        <v>-0.4595412875201066</v>
+        <v>-4.024253960568839</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>10.7318544439227</v>
       </c>
       <c r="E26">
-        <v>-31.44551954040321</v>
+        <v>-33.13042660020012</v>
       </c>
       <c r="F26">
-        <v>1.627766344536517</v>
+        <v>0.3558438208166755</v>
       </c>
       <c r="G26">
-        <v>-0.6445047773447271</v>
+        <v>-2.581935343292404</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>10.2763446134108</v>
       </c>
       <c r="E27">
-        <v>-31.73129568536826</v>
+        <v>-32.38856519555255</v>
       </c>
       <c r="F27">
-        <v>1.391312716537745</v>
+        <v>1.229736704220951</v>
       </c>
       <c r="G27">
-        <v>-0.1010290688902727</v>
+        <v>-2.428451831000713</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>9.767035732222594</v>
       </c>
       <c r="E28">
-        <v>-31.07502923217668</v>
+        <v>-31.44599050170001</v>
       </c>
       <c r="F28">
-        <v>1.789342356853311</v>
+        <v>0.6856972970314459</v>
       </c>
       <c r="G28">
-        <v>0.1919475902441488</v>
+        <v>-2.363833292619679</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>9.228471696218698</v>
       </c>
       <c r="E29">
-        <v>-32.07472836139898</v>
+        <v>-33.33820657309406</v>
       </c>
       <c r="F29">
-        <v>1.41334840064517</v>
+        <v>1.066906396819129</v>
       </c>
       <c r="G29">
-        <v>-0.4753359002879695</v>
+        <v>-1.827716926899024</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.687704109283866</v>
       </c>
       <c r="E30">
-        <v>-30.37284405254731</v>
+        <v>-31.8574227434299</v>
       </c>
       <c r="F30">
-        <v>1.23157063567103</v>
+        <v>0.6300316178096648</v>
       </c>
       <c r="G30">
-        <v>-0.0727901154402895</v>
+        <v>-4.244163569106006</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>8.157705326589731</v>
       </c>
       <c r="E31">
-        <v>-29.43064748627441</v>
+        <v>-34.11676220262579</v>
       </c>
       <c r="F31">
-        <v>1.580537066726281</v>
+        <v>0.5785754289111217</v>
       </c>
       <c r="G31">
-        <v>-0.424863322996241</v>
+        <v>-3.120756424718643</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>7.657586878255517</v>
       </c>
       <c r="E32">
-        <v>-31.29925435842947</v>
+        <v>-31.37256808837665</v>
       </c>
       <c r="F32">
-        <v>1.413449757823758</v>
+        <v>1.378912299219855</v>
       </c>
       <c r="G32">
-        <v>-1.001649740666842</v>
+        <v>-3.531714305781611</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>7.19555159686985</v>
       </c>
       <c r="E33">
-        <v>-31.53252284727558</v>
+        <v>-30.71356870112143</v>
       </c>
       <c r="F33">
-        <v>1.554773338893912</v>
+        <v>0.5541475570184259</v>
       </c>
       <c r="G33">
-        <v>-1.41615321600237</v>
+        <v>-2.927351043768881</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.773263279767479</v>
       </c>
       <c r="E34">
-        <v>-29.16631819420969</v>
+        <v>-30.49617930638322</v>
       </c>
       <c r="F34">
-        <v>2.152189970257389</v>
+        <v>0.8935650332565351</v>
       </c>
       <c r="G34">
-        <v>-0.769484492543293</v>
+        <v>-3.453986007065063</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.395371784462056</v>
       </c>
       <c r="E35">
-        <v>-29.29261280580961</v>
+        <v>-32.03488005436848</v>
       </c>
       <c r="F35">
-        <v>2.077165069925276</v>
+        <v>0.3115190596553563</v>
       </c>
       <c r="G35">
-        <v>-1.933839774705902</v>
+        <v>-4.666655390827795</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.051221803170839</v>
       </c>
       <c r="E36">
-        <v>-28.95309499555853</v>
+        <v>-31.64377839669603</v>
       </c>
       <c r="F36">
-        <v>1.718824683556539</v>
+        <v>1.325436885279126</v>
       </c>
       <c r="G36">
-        <v>-2.049702247489314</v>
+        <v>-4.917932418349557</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.735728651093022</v>
       </c>
       <c r="E37">
-        <v>-28.71717961365493</v>
+        <v>-31.36301300822047</v>
       </c>
       <c r="F37">
-        <v>2.127238683559641</v>
+        <v>0.8220116162910655</v>
       </c>
       <c r="G37">
-        <v>-1.421844043784377</v>
+        <v>-3.657938786102943</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.439560740942452</v>
       </c>
       <c r="E38">
-        <v>-27.26005253220685</v>
+        <v>-31.69646266330126</v>
       </c>
       <c r="F38">
-        <v>2.396153531707174</v>
+        <v>0.9564634973941283</v>
       </c>
       <c r="G38">
-        <v>-3.118170888652472</v>
+        <v>-3.897046248222344</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.148193641972869</v>
       </c>
       <c r="E39">
-        <v>-26.7147472776252</v>
+        <v>-28.38683196326939</v>
       </c>
       <c r="F39">
-        <v>2.189616108451054</v>
+        <v>1.021805619759244</v>
       </c>
       <c r="G39">
-        <v>-2.047778820530998</v>
+        <v>-3.547293733089421</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.860212323931455</v>
       </c>
       <c r="E40">
-        <v>-26.39751408796587</v>
+        <v>-26.18676796459691</v>
       </c>
       <c r="F40">
-        <v>2.294020337220484</v>
+        <v>1.675157160350127</v>
       </c>
       <c r="G40">
-        <v>-3.464775074977548</v>
+        <v>-4.045650016389149</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.565421097644101</v>
       </c>
       <c r="E41">
-        <v>-26.45625292431937</v>
+        <v>-27.23506441263252</v>
       </c>
       <c r="F41">
-        <v>2.242556229792364</v>
+        <v>1.320435541998168</v>
       </c>
       <c r="G41">
-        <v>-3.638548920879431</v>
+        <v>-7.332988631430045</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.261792086544564</v>
       </c>
       <c r="E42">
-        <v>-27.19885473446719</v>
+        <v>-26.03309872762062</v>
       </c>
       <c r="F42">
-        <v>2.863644513473913</v>
+        <v>1.737157663233666</v>
       </c>
       <c r="G42">
-        <v>-3.091795772341099</v>
+        <v>-5.472879167097586</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.947175948538811</v>
       </c>
       <c r="E43">
-        <v>-24.93101759379591</v>
+        <v>-24.51265905107129</v>
       </c>
       <c r="F43">
-        <v>3.31209618272524</v>
+        <v>2.017790351449536</v>
       </c>
       <c r="G43">
-        <v>-4.631404701925636</v>
+        <v>-5.859335700624408</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.61238493773651</v>
       </c>
       <c r="E44">
-        <v>-22.30348829116939</v>
+        <v>-25.38853385126486</v>
       </c>
       <c r="F44">
-        <v>2.574516826727626</v>
+        <v>1.650674650603348</v>
       </c>
       <c r="G44">
-        <v>-4.923692767587888</v>
+        <v>-6.166743027764513</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.259903562571837</v>
       </c>
       <c r="E45">
-        <v>-22.18155912851286</v>
+        <v>-26.11147302727137</v>
       </c>
       <c r="F45">
-        <v>3.30748126368765</v>
+        <v>1.634501845794881</v>
       </c>
       <c r="G45">
-        <v>-5.472455417268559</v>
+        <v>-6.159108909750953</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.880669389625773</v>
       </c>
       <c r="E46">
-        <v>-21.05605219864647</v>
+        <v>-21.76225413472064</v>
       </c>
       <c r="F46">
-        <v>3.373447366183449</v>
+        <v>1.704878569265179</v>
       </c>
       <c r="G46">
-        <v>-5.502836293682451</v>
+        <v>-7.170828179279924</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.46993846792319</v>
       </c>
       <c r="E47">
-        <v>-22.16329126436592</v>
+        <v>-23.39093792547531</v>
       </c>
       <c r="F47">
-        <v>3.122106902579547</v>
+        <v>1.486023081398771</v>
       </c>
       <c r="G47">
-        <v>-4.700581861514246</v>
+        <v>-6.958350745478421</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.025016678132562</v>
       </c>
       <c r="E48">
-        <v>-19.92029280362672</v>
+        <v>-21.39130418638232</v>
       </c>
       <c r="F48">
-        <v>3.301225625321664</v>
+        <v>1.749041792423123</v>
       </c>
       <c r="G48">
-        <v>-6.302693890880223</v>
+        <v>-7.842829197205504</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.535095191378947</v>
       </c>
       <c r="E49">
-        <v>-19.95972675528551</v>
+        <v>-22.65445861218586</v>
       </c>
       <c r="F49">
-        <v>3.232782606774117</v>
+        <v>1.840325017683138</v>
       </c>
       <c r="G49">
-        <v>-5.809651033171026</v>
+        <v>-5.677146447961697</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.004774951652414</v>
       </c>
       <c r="E50">
-        <v>-19.03418818064982</v>
+        <v>-22.66924860829491</v>
       </c>
       <c r="F50">
-        <v>3.271586569114215</v>
+        <v>2.28256539233411</v>
       </c>
       <c r="G50">
-        <v>-5.967133684474156</v>
+        <v>-7.46401340278332</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.4291331830348959</v>
       </c>
       <c r="E51">
-        <v>-17.89350180590972</v>
+        <v>-19.89821196436531</v>
       </c>
       <c r="F51">
-        <v>3.375719984172104</v>
+        <v>2.393070056289814</v>
       </c>
       <c r="G51">
-        <v>-6.860351976424916</v>
+        <v>-7.022432975482094</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.1905813575294786</v>
       </c>
       <c r="E52">
-        <v>-17.66281228301098</v>
+        <v>-18.59046112653424</v>
       </c>
       <c r="F52">
-        <v>3.569872827169488</v>
+        <v>2.094056877219353</v>
       </c>
       <c r="G52">
-        <v>-6.931181098237622</v>
+        <v>-8.032841268977513</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.8436787065640119</v>
       </c>
       <c r="E53">
-        <v>-18.30949648520234</v>
+        <v>-19.88326800014</v>
       </c>
       <c r="F53">
-        <v>3.389588496873608</v>
+        <v>2.294373503639627</v>
       </c>
       <c r="G53">
-        <v>-7.889474783853835</v>
+        <v>-7.086899228768321</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.529299475024575</v>
       </c>
       <c r="E54">
-        <v>-16.69890394810831</v>
+        <v>-18.86109631865464</v>
       </c>
       <c r="F54">
-        <v>3.963301801800702</v>
+        <v>2.090077024253854</v>
       </c>
       <c r="G54">
-        <v>-7.710188879629064</v>
+        <v>-7.938980681848096</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.231637109188306</v>
       </c>
       <c r="E55">
-        <v>-15.16293160571267</v>
+        <v>-18.0054275694833</v>
       </c>
       <c r="F55">
-        <v>3.431895616698657</v>
+        <v>2.191050946010442</v>
       </c>
       <c r="G55">
-        <v>-7.846974000220672</v>
+        <v>-7.851559105792562</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.942018417235762</v>
       </c>
       <c r="E56">
-        <v>-14.16251018488615</v>
+        <v>-19.03781095985596</v>
       </c>
       <c r="F56">
-        <v>3.843100106524763</v>
+        <v>2.363678058205173</v>
       </c>
       <c r="G56">
-        <v>-7.765090966852338</v>
+        <v>-7.312926725462061</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.651597857762001</v>
       </c>
       <c r="E57">
-        <v>-14.54659270784671</v>
+        <v>-16.5498265837758</v>
       </c>
       <c r="F57">
-        <v>3.7941651774436</v>
+        <v>1.804579191465754</v>
       </c>
       <c r="G57">
-        <v>-7.568149923266635</v>
+        <v>-8.924920733262763</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.340336789162292</v>
       </c>
       <c r="E58">
-        <v>-13.64609659447344</v>
+        <v>-16.77048100827354</v>
       </c>
       <c r="F58">
-        <v>3.378475632464969</v>
+        <v>2.324604865859451</v>
       </c>
       <c r="G58">
-        <v>-8.892143021878439</v>
+        <v>-7.296311097400459</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.00316527071383</v>
       </c>
       <c r="E59">
-        <v>-13.40001931689663</v>
+        <v>-17.09898556973797</v>
       </c>
       <c r="F59">
-        <v>4.036513358859636</v>
+        <v>1.892918307428966</v>
       </c>
       <c r="G59">
-        <v>-9.77526414993442</v>
+        <v>-9.284025539544126</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.625576773002642</v>
       </c>
       <c r="E60">
-        <v>-13.23873771511346</v>
+        <v>-16.0725571226854</v>
       </c>
       <c r="F60">
-        <v>4.132647475338642</v>
+        <v>2.122585755580079</v>
       </c>
       <c r="G60">
-        <v>-8.60342372430752</v>
+        <v>-8.217172444604133</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.19767996683762</v>
       </c>
       <c r="E61">
-        <v>-13.86965377081011</v>
+        <v>-16.1991415566218</v>
       </c>
       <c r="F61">
-        <v>3.614395551570238</v>
+        <v>1.608966171614335</v>
       </c>
       <c r="G61">
-        <v>-9.480887130036887</v>
+        <v>-9.599308654522156</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.714070227542652</v>
       </c>
       <c r="E62">
-        <v>-13.56866421741629</v>
+        <v>-15.35274259374417</v>
       </c>
       <c r="F62">
-        <v>3.882768772294691</v>
+        <v>1.730401573798401</v>
       </c>
       <c r="G62">
-        <v>-9.657938416022649</v>
+        <v>-9.159214662168063</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.159931586413909</v>
       </c>
       <c r="E63">
-        <v>-12.18449990917978</v>
+        <v>-15.35052816995442</v>
       </c>
       <c r="F63">
-        <v>3.634511784108149</v>
+        <v>2.345289648821006</v>
       </c>
       <c r="G63">
-        <v>-9.167196387463246</v>
+        <v>-9.155847837354624</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.533295096425263</v>
       </c>
       <c r="E64">
-        <v>-11.69157098497085</v>
+        <v>-13.23701689499054</v>
       </c>
       <c r="F64">
-        <v>3.359642201718563</v>
+        <v>1.997897421445701</v>
       </c>
       <c r="G64">
-        <v>-10.14733967363865</v>
+        <v>-11.34305906424031</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.826390616569278</v>
       </c>
       <c r="E65">
-        <v>-10.91201229844643</v>
+        <v>-13.16255972535642</v>
       </c>
       <c r="F65">
-        <v>3.377059799376566</v>
+        <v>2.481486773842883</v>
       </c>
       <c r="G65">
-        <v>-9.639359634456261</v>
+        <v>-10.28494912006953</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.035235273653521</v>
       </c>
       <c r="E66">
-        <v>-12.17751247378595</v>
+        <v>-15.50176108791458</v>
       </c>
       <c r="F66">
-        <v>3.141439200689316</v>
+        <v>1.702178350679354</v>
       </c>
       <c r="G66">
-        <v>-9.215487315244594</v>
+        <v>-10.24564632342731</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.16177050251879</v>
       </c>
       <c r="E67">
-        <v>-11.27893190491792</v>
+        <v>-14.8089543779551</v>
       </c>
       <c r="F67">
-        <v>3.553212240939065</v>
+        <v>1.298901892665938</v>
       </c>
       <c r="G67">
-        <v>-9.646884504467023</v>
+        <v>-9.20660181101719</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.205190091021047</v>
       </c>
       <c r="E68">
-        <v>-10.48167594197153</v>
+        <v>-12.04800264564058</v>
       </c>
       <c r="F68">
-        <v>3.066830815012964</v>
+        <v>1.369459158610596</v>
       </c>
       <c r="G68">
-        <v>-9.830503912802699</v>
+        <v>-9.8385882650096</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.173787000546614</v>
       </c>
       <c r="E69">
-        <v>-11.75474319737786</v>
+        <v>-16.10896605370706</v>
       </c>
       <c r="F69">
-        <v>2.998745714002307</v>
+        <v>1.635296866164431</v>
       </c>
       <c r="G69">
-        <v>-10.81299768631098</v>
+        <v>-10.4042049020307</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.071501590571593</v>
       </c>
       <c r="E70">
-        <v>-10.83304476870068</v>
+        <v>-15.18893863193872</v>
       </c>
       <c r="F70">
-        <v>2.755534412862355</v>
+        <v>1.566516518256896</v>
       </c>
       <c r="G70">
-        <v>-10.1017964986549</v>
+        <v>-10.18163361487996</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.907791787547972</v>
       </c>
       <c r="E71">
-        <v>-10.64519008144049</v>
+        <v>-14.29107809043792</v>
       </c>
       <c r="F71">
-        <v>2.172103488438125</v>
+        <v>0.893279966191756</v>
       </c>
       <c r="G71">
-        <v>-10.34739594057681</v>
+        <v>-9.834718237274192</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.691379267654421</v>
       </c>
       <c r="E72">
-        <v>-10.92325649940748</v>
+        <v>-12.59832997789673</v>
       </c>
       <c r="F72">
-        <v>2.234227520383068</v>
+        <v>1.318269032305847</v>
       </c>
       <c r="G72">
-        <v>-10.54743234424173</v>
+        <v>-11.05173436732999</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.429688427046828</v>
       </c>
       <c r="E73">
-        <v>-11.00978658074604</v>
+        <v>-15.55739791957282</v>
       </c>
       <c r="F73">
-        <v>2.355940071102335</v>
+        <v>1.393183073223879</v>
       </c>
       <c r="G73">
-        <v>-9.959009359000589</v>
+        <v>-10.42173755120668</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.134425272015937</v>
       </c>
       <c r="E74">
-        <v>-11.20331544593784</v>
+        <v>-12.41026698083219</v>
       </c>
       <c r="F74">
-        <v>2.86955965506808</v>
+        <v>1.366914143204485</v>
       </c>
       <c r="G74">
-        <v>-10.3805676068803</v>
+        <v>-9.910523109032424</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.810792107904565</v>
       </c>
       <c r="E75">
-        <v>-10.15029127103823</v>
+        <v>-16.20046387103205</v>
       </c>
       <c r="F75">
-        <v>2.570460955878186</v>
+        <v>1.035398567631461</v>
       </c>
       <c r="G75">
-        <v>-9.226488258071592</v>
+        <v>-8.940182348198803</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.470158379445163</v>
       </c>
       <c r="E76">
-        <v>-10.68389494878405</v>
+        <v>-14.26199170188665</v>
       </c>
       <c r="F76">
-        <v>2.602689371257379</v>
+        <v>1.161784634507191</v>
       </c>
       <c r="G76">
-        <v>-9.603933486640519</v>
+        <v>-8.7660443422876</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.12043373192105</v>
       </c>
       <c r="E77">
-        <v>-11.18585365016427</v>
+        <v>-13.27720710180861</v>
       </c>
       <c r="F77">
-        <v>2.07577457613152</v>
+        <v>1.199326383232683</v>
       </c>
       <c r="G77">
-        <v>-9.73738157732854</v>
+        <v>-10.02316773155166</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.766704174686306</v>
       </c>
       <c r="E78">
-        <v>-12.43711177474966</v>
+        <v>-14.75137935942158</v>
       </c>
       <c r="F78">
-        <v>2.330716386987131</v>
+        <v>0.2265516535861145</v>
       </c>
       <c r="G78">
-        <v>-8.492729013110909</v>
+        <v>-10.07233264335538</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.418802954057278</v>
       </c>
       <c r="E79">
-        <v>-11.12910281390014</v>
+        <v>-14.91939480205416</v>
       </c>
       <c r="F79">
-        <v>1.743747463547809</v>
+        <v>0.6347130524957038</v>
       </c>
       <c r="G79">
-        <v>-9.038111595795984</v>
+        <v>-9.099469246820837</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.07748184121686</v>
       </c>
       <c r="E80">
-        <v>-12.38555962664634</v>
+        <v>-16.1785324714129</v>
       </c>
       <c r="F80">
-        <v>2.188024484006037</v>
+        <v>-0.2510370370974671</v>
       </c>
       <c r="G80">
-        <v>-8.93928519035766</v>
+        <v>-10.52522189421876</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.747904319387771</v>
       </c>
       <c r="E81">
-        <v>-13.01509902624465</v>
+        <v>-15.27444980662556</v>
       </c>
       <c r="F81">
-        <v>2.199883273900848</v>
+        <v>0.7027268867401663</v>
       </c>
       <c r="G81">
-        <v>-8.901223848292659</v>
+        <v>-9.643335599648925</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.431984222215767</v>
       </c>
       <c r="E82">
-        <v>-15.00566676037429</v>
+        <v>-16.36986049823697</v>
       </c>
       <c r="F82">
-        <v>2.402692653432024</v>
+        <v>0.3051723581992327</v>
       </c>
       <c r="G82">
-        <v>-7.973966527107114</v>
+        <v>-8.403039713360974</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.124643652214131</v>
       </c>
       <c r="E83">
-        <v>-14.62909697579245</v>
+        <v>-14.37672511934498</v>
       </c>
       <c r="F83">
-        <v>2.076732718210361</v>
+        <v>0.5335902623830642</v>
       </c>
       <c r="G83">
-        <v>-8.373685106064256</v>
+        <v>-6.694728693640717</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.829062609410583</v>
       </c>
       <c r="E84">
-        <v>-16.51079113782968</v>
+        <v>-17.22597303786106</v>
       </c>
       <c r="F84">
-        <v>2.085842194635969</v>
+        <v>0.7529557035542438</v>
       </c>
       <c r="G84">
-        <v>-7.339639517418441</v>
+        <v>-8.273802636598905</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.538629056386409</v>
       </c>
       <c r="E85">
-        <v>-17.00925385727598</v>
+        <v>-19.50209275749236</v>
       </c>
       <c r="F85">
-        <v>1.494470568751725</v>
+        <v>1.262756972557864</v>
       </c>
       <c r="G85">
-        <v>-6.514919723220742</v>
+        <v>-9.364647255061998</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.25118048268898</v>
       </c>
       <c r="E86">
-        <v>-18.74148120621604</v>
+        <v>-21.17779569386868</v>
       </c>
       <c r="F86">
-        <v>1.888856101755864</v>
+        <v>0.9145222136355453</v>
       </c>
       <c r="G86">
-        <v>-6.475643410942828</v>
+        <v>-7.589026223437278</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.965064719282383</v>
       </c>
       <c r="E87">
-        <v>-19.25478826345948</v>
+        <v>-23.22496482462019</v>
       </c>
       <c r="F87">
-        <v>1.891342520043104</v>
+        <v>0.6052798780572617</v>
       </c>
       <c r="G87">
-        <v>-6.76952715955501</v>
+        <v>-7.535739682437169</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.673648451022991</v>
       </c>
       <c r="E88">
-        <v>-19.47334147601767</v>
+        <v>-20.92046515838281</v>
       </c>
       <c r="F88">
-        <v>1.819169874064697</v>
+        <v>0.1818317577988931</v>
       </c>
       <c r="G88">
-        <v>-5.492616639602721</v>
+        <v>-6.457352646838356</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.38096880674587</v>
       </c>
       <c r="E89">
-        <v>-22.17549550181659</v>
+        <v>-23.80246752939637</v>
       </c>
       <c r="F89">
-        <v>1.597294259017546</v>
+        <v>0.6006190315481233</v>
       </c>
       <c r="G89">
-        <v>-6.023783739742165</v>
+        <v>-6.791403244478515</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.086027982163928</v>
       </c>
       <c r="E90">
-        <v>-21.98758647286831</v>
+        <v>-25.75839696584133</v>
       </c>
       <c r="F90">
-        <v>1.315508632895236</v>
+        <v>0.107680271279145</v>
       </c>
       <c r="G90">
-        <v>-5.736064226924106</v>
+        <v>-7.990363659163124</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.791637725983002</v>
       </c>
       <c r="E91">
-        <v>-23.09506101923616</v>
+        <v>-24.74640529392521</v>
       </c>
       <c r="F91">
-        <v>1.316862701452937</v>
+        <v>0.1663534080343456</v>
       </c>
       <c r="G91">
-        <v>-6.098592137293076</v>
+        <v>-6.878695709258017</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.504538466260931</v>
       </c>
       <c r="E92">
-        <v>-24.90723857678163</v>
+        <v>-29.46372119618943</v>
       </c>
       <c r="F92">
-        <v>1.356742000109618</v>
+        <v>-0.1987185203279672</v>
       </c>
       <c r="G92">
-        <v>-5.203364344199979</v>
+        <v>-7.037658174417201</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.226366986853013</v>
       </c>
       <c r="E93">
-        <v>-26.37398866549603</v>
+        <v>-28.56910757055213</v>
       </c>
       <c r="F93">
-        <v>1.087223760008302</v>
+        <v>-0.4206068050224419</v>
       </c>
       <c r="G93">
-        <v>-5.761873239948264</v>
+        <v>-5.713797497626968</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.964565050033399</v>
       </c>
       <c r="E94">
-        <v>-26.8142242661517</v>
+        <v>-31.54955217378143</v>
       </c>
       <c r="F94">
-        <v>0.925490960805879</v>
+        <v>0.02824158256070229</v>
       </c>
       <c r="G94">
-        <v>-5.440233877534832</v>
+        <v>-7.765071103579102</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.7213636896669059</v>
       </c>
       <c r="E95">
-        <v>-30.52451170401221</v>
+        <v>-31.49182092289464</v>
       </c>
       <c r="F95">
-        <v>0.3133403214581116</v>
+        <v>-0.5720811491576056</v>
       </c>
       <c r="G95">
-        <v>-4.897463315280243</v>
+        <v>-5.939421107764917</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.4981039786700382</v>
       </c>
       <c r="E96">
-        <v>-31.99141349660585</v>
+        <v>-35.77397990810279</v>
       </c>
       <c r="F96">
-        <v>0.5863007463666353</v>
+        <v>-0.2594021717428182</v>
       </c>
       <c r="G96">
-        <v>-4.491689748531773</v>
+        <v>-5.535236602875298</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.2978675982230786</v>
       </c>
       <c r="E97">
-        <v>-35.12214909520171</v>
+        <v>-35.65654752013588</v>
       </c>
       <c r="F97">
-        <v>0.2563577907676426</v>
+        <v>0.2534469392950649</v>
       </c>
       <c r="G97">
-        <v>-5.268161652040134</v>
+        <v>-6.738705980584395</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.1211334930601239</v>
       </c>
       <c r="E98">
-        <v>-35.52944231168859</v>
+        <v>-38.96082103541668</v>
       </c>
       <c r="F98">
-        <v>0.216430189080541</v>
+        <v>-0.4541219814579291</v>
       </c>
       <c r="G98">
-        <v>-4.57614838632966</v>
+        <v>-7.729462875758702</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.03258605038084204</v>
       </c>
       <c r="E99">
-        <v>-38.06360806569897</v>
+        <v>-41.29264098534233</v>
       </c>
       <c r="F99">
-        <v>-0.08454361791323339</v>
+        <v>-0.5196351440619128</v>
       </c>
       <c r="G99">
-        <v>-5.21807971912204</v>
+        <v>-7.267744399942088</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.1577428509344754</v>
       </c>
       <c r="E100">
-        <v>-41.25196396756843</v>
+        <v>-41.97407896130555</v>
       </c>
       <c r="F100">
-        <v>-0.6017613817188562</v>
+        <v>-1.54186742574174</v>
       </c>
       <c r="G100">
-        <v>-5.04478259177781</v>
+        <v>-7.755450658241981</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.2640954146981978</v>
       </c>
       <c r="E101">
-        <v>-42.23571607557272</v>
+        <v>-44.32105797797188</v>
       </c>
       <c r="F101">
-        <v>-0.5158817610423213</v>
+        <v>-1.079746790734255</v>
       </c>
       <c r="G101">
-        <v>-3.772688915585161</v>
+        <v>-6.904176978273787</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.3360726455952007</v>
       </c>
       <c r="E102">
-        <v>-44.19839293828911</v>
+        <v>-45.79810128810571</v>
       </c>
       <c r="F102">
-        <v>-0.06769061141408451</v>
+        <v>-1.020843224768358</v>
       </c>
       <c r="G102">
-        <v>-5.416073516189232</v>
+        <v>-7.409948883581482</v>
       </c>
     </row>
   </sheetData>
